--- a/reports/pdf_change_20261027.xlsx
+++ b/reports/pdf_change_20261027.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,14 +553,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 10/10  ·  전일분: RISE, TIGER 기술이전, TIGER 코스닥, MIDAS  ·  전부 반영 완료</t>
+          <t>캡처 10/10  ·  전부 반영 완료</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,331억   ·   현금 7억(0.2%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 3종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,121억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -656,7 +656,7 @@
         <v>170</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4706094326</v>
+        <v>4701359163</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>-72</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-669876669</v>
+        <v>-669202654</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>92</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>827604633</v>
+        <v>826771917</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>-44</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1863154125</v>
+        <v>-1861279462</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>79</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1470007134</v>
+        <v>1468528047</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>-14</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-821044231</v>
+        <v>-820218116</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>-8</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1916432540</v>
+        <v>-1914504270</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>-4</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-792417023</v>
+        <v>-791619712</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억   ·   현금 62억(2.1%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,996억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -861,7 +861,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,181억   ·   현금 32억(1.6%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 4종목  /  매도 7종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,019억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 4종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -957,7 +957,7 @@
         <v>125</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>6484503537</v>
+        <v>6504145284</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>-100</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-2385901301</v>
+        <v>-2393128265</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>104</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1709136932</v>
+        <v>1714313957</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>-70</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-3169321729</v>
+        <v>-3178921695</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>70</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2196811198</v>
+        <v>2203465402</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>-25</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1011450552</v>
+        <v>-1014514264</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2440351331</v>
+        <v>2447743225</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1103,23 +1103,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2081641135</v>
+        <v>-2219022391</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.43%→5.25%</t>
+          <t>3.34%→2.23%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>120→100</t>
+          <t>60→40</t>
         </is>
       </c>
     </row>
@@ -1131,23 +1131,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-2212321207</v>
+        <v>-2087946486</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>3.34%→2.23%</t>
+          <t>6.43%→5.25%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>60→40</t>
+          <t>120→100</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-110286060</v>
+        <v>-110620120</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-31020017</v>
+        <v>-31113977</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,148억   ·   현금 1억(0.0%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,079억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1234,7 +1234,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억   ·   현금 2억(0.9%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 1종목  /  매도 1종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 233억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1330,11 +1330,11 @@
         <v>77</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>74412753</v>
+        <v>71800960</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>3.25%→3.56%</t>
+          <t>3.28%→3.60%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1351,11 +1351,11 @@
         <v>-67</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-101625536</v>
+        <v>-119420800</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>5.23%→4.81%</t>
+          <t>6.43%→5.92%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 425억   ·   현금 -2억(-0.4%)      ※전일분  PDF 2026-10-26  vs  2026-10-23      매수 2종목  /  매도 8종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 414억   ·   현금 -2억(-0.4%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1382,190 +1382,98 @@
       <c r="K34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억   ·   현금 69억(6.6%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>521413017</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>2.65%→3.92%</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>119→173</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱  (편출)</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>-179</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>-345677519</v>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>0.80%→0.00%</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>179→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>삼성바이오로직스</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>1838363355</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>2.52%→7.05%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>7→18</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>큐라클  (편출)</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-99</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>-100219645</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>0.23%→0.00%</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>99→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="n"/>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-53</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-412064255</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>5.45%→4.45%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>297→244</t>
         </is>
       </c>
     </row>
@@ -1577,459 +1485,544 @@
       <c r="E40" s="17" t="n"/>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-48</v>
+        <v>-3</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-491932627</v>
+        <v>-507847568</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>4.56%→3.46%</t>
+          <t>2.08%→1.58%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>192→144</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="17" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-98723965</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>4.37%→4.39%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>798→758</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="n"/>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="17" t="n"/>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>프로티나</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-31</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-153552246</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>5.25%→5.03%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>464→433</t>
-        </is>
-      </c>
+          <t>12→9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 799억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 4종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n"/>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="17" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>휴젤  (편출)</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-21</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-432835048</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>1.00%→0.00%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>21→0</t>
-        </is>
-      </c>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n"/>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="17" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>파마리서치</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-327635885</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>3.64%→2.69%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>54→42</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 58억(5.4%)      ※전일분  PDF 2026-10-26  vs  2026-10-23      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>152</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>624355497</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>1.32%→2.10%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>256→408</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>엠케이전자</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-166</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-367006255</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>1.97%→1.50%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>706→540</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>RFHIC</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>950544453</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>0.80%→2.08%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>89→209</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-131</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-719661943</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>2.98%→1.70%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>377→246</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억   ·   현금 2억(0.2%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 4종목  /  매도 5종목</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>252907320</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>3.61%→3.82%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>574→626</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>SFA  (편출)</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-97</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-413918597</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.49%→0.00%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>97→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>125563260</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>5.54%→5.47%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>1,247→1,284</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>태웅  (편출)</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-161515277</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>0.19%→0.00%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>38→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이  (편출)</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-251076120</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>7→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 281억   ·   현금 2억(0.7%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 3종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>에프에스티</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>152</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>628071451</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>1.32%→2.10%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>256→408</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>엠케이전자</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-166</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-369190553</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>1.97%→1.50%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>706→540</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>RFHIC</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>956201774</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>0.80%→2.08%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>89→209</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-131</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-723945129</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>2.98%→1.70%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>377→246</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>루닛  (신규)</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>254412540</v>
+        <v>380838519</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>3.61%→3.82%</t>
+          <t>0.00%→1.36%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>574→626</t>
+          <t>0→61</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>SFA  (편출)</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-97</v>
+        <v>-19</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-416382101</v>
+        <v>-103279323</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.00%</t>
+          <t>2.57%→1.93%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>97→0</t>
+          <t>118→99</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>126310570</v>
+        <v>151325607</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>5.54%→5.47%</t>
+          <t>2.38%→3.08%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>1,247→1,284</t>
+          <t>178→216</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>태웅  (편출)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-38</v>
+        <v>-15</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-162476562</v>
+        <v>-199856391</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.19%→0.00%</t>
+          <t>4.29%→3.58%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>38→0</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>198050140</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>1.19%→2.06%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>19→29</t>
+        </is>
+      </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>티씨케이  (편출)</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-252570440</v>
+        <v>-107546326</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>0.93%→0.49%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>7→0</t>
+          <t>16→9</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억   ·   현금 4억(1.4%)      ※전일분  PDF 2026-10-26  vs  2026-10-23      매수 3종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 53억   ·   현금 1억(1.8%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2044,180 +2037,7 @@
       <c r="K58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>HT로보틱스  (재편입·10/21까지 25주)</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C61" s="11" t="n">
-        <v>11742753</v>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.04%</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>0→3</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="n"/>
-      <c r="H61" s="17" t="n"/>
-      <c r="I61" s="17" t="n"/>
-      <c r="J61" s="17" t="n"/>
-      <c r="K61" s="17" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>피노</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>8772002</v>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>2.85%→2.69%</t>
-        </is>
-      </c>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>269→272</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="n"/>
-      <c r="H62" s="17" t="n"/>
-      <c r="I62" s="17" t="n"/>
-      <c r="J62" s="17" t="n"/>
-      <c r="K62" s="17" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>피엠티  (재편입·10/21까지 53주)</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" s="11" t="n">
-        <v>4277626</v>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.01%</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>0→3</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="n"/>
-      <c r="H63" s="17" t="n"/>
-      <c r="I63" s="17" t="n"/>
-      <c r="J63" s="17" t="n"/>
-      <c r="K63" s="17" t="n"/>
-    </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      ※전일분  PDF 2026-10-26  vs  2026-10-23      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -2228,30 +2048,30 @@
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A58:K58"/>
     <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="G59:K59"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="G43:K43"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="A37:K37"/>
     <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A50:E50"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="G30:K30"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A42:K42"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="G16:K16"/>
-    <mergeCell ref="G50:K50"/>
     <mergeCell ref="A13:K13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20261027.xlsx
+++ b/reports/pdf_change_20261027.xlsx
@@ -1367,7 +1367,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 414억   ·   현금 -2억(-0.4%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 414억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1391,7 +1391,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억   ·   현금 69억(6.6%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 1종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1801,7 +1801,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 281억   ·   현금 2억(0.7%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 3종목  /  매도 3종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 281억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2022,7 +2022,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 53억   ·   현금 1억(1.8%)      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 53억      당일 2026-10-27  vs  전영업일 2026-10-26      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>

--- a/reports/pdf_change_20261027.xlsx
+++ b/reports/pdf_change_20261027.xlsx
@@ -1103,23 +1103,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2219022391</v>
+        <v>-2087946486</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.34%→2.23%</t>
+          <t>6.43%→5.25%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>60→40</t>
+          <t>120→100</t>
         </is>
       </c>
     </row>
@@ -1131,23 +1131,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-2087946486</v>
+        <v>-2219022391</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>6.43%→5.25%</t>
+          <t>3.34%→2.23%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>120→100</t>
+          <t>60→40</t>
         </is>
       </c>
     </row>
